--- a/CLAMS/CLAMS_PARENTS_4K.xlsx
+++ b/CLAMS/CLAMS_PARENTS_4K.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\ID_MOLLUSCS\FINAL RESULTS\CLAMS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\ID_MOLLUSCS\FINAL RESULTS\CLAMS\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -15,6 +15,9 @@
     <sheet name="Inbreeding parents clams" sheetId="1" r:id="rId1"/>
     <sheet name="Coancestry parents clams" sheetId="10" r:id="rId2"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId3"/>
+  </externalReferences>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -2101,7 +2104,8 @@
         <c:axId val="498062240"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:min val="0"/>
+          <c:max val="0.15000000000000002"/>
+          <c:min val="-0.1"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
@@ -2198,7 +2202,7 @@
         <c:crossAx val="498062656"/>
         <c:crossesAt val="-0.25"/>
         <c:crossBetween val="midCat"/>
-        <c:majorUnit val="2.5000000000000005E-2"/>
+        <c:majorUnit val="5.000000000000001E-2"/>
       </c:valAx>
       <c:valAx>
         <c:axId val="498062656"/>
@@ -2666,8 +2670,8 @@
             <c:trendlineLbl>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="-7.1188629233459533E-2"/>
-                  <c:y val="-0.36564085739282592"/>
+                  <c:x val="-7.3222019991629597E-2"/>
+                  <c:y val="-0.38724579566443085"/>
                 </c:manualLayout>
               </c:layout>
               <c:numFmt formatCode="General" sourceLinked="0"/>
@@ -3130,8 +3134,8 @@
             <c:trendlineLbl>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="-0.14977078730424456"/>
-                  <c:y val="-0.32160906969962089"/>
+                  <c:x val="-0.10853667240915034"/>
+                  <c:y val="-0.34012758821813938"/>
                 </c:manualLayout>
               </c:layout>
               <c:numFmt formatCode="General" sourceLinked="0"/>
@@ -3453,7 +3457,8 @@
         <c:axId val="498062240"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:min val="0"/>
+          <c:max val="0.15000000000000002"/>
+          <c:min val="-0.1"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
@@ -3550,7 +3555,7 @@
         <c:crossAx val="498062656"/>
         <c:crossesAt val="-0.25"/>
         <c:crossBetween val="midCat"/>
-        <c:majorUnit val="2.5000000000000005E-2"/>
+        <c:majorUnit val="5.000000000000001E-2"/>
       </c:valAx>
       <c:valAx>
         <c:axId val="498062656"/>
@@ -3720,8 +3725,8 @@
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.61367862855214794"/>
-          <c:y val="0.14732186254495963"/>
+          <c:x val="0.59719737597695222"/>
+          <c:y val="0.12571692427335471"/>
           <c:w val="0.17298366836131215"/>
           <c:h val="0.1713283756197142"/>
         </c:manualLayout>
@@ -5599,6 +5604,19 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="DATOS"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
